--- a/hearts-prototype/artifacts/hearts-master-sheet-example.xlsx
+++ b/hearts-prototype/artifacts/hearts-master-sheet-example.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="386">
   <si>
     <t>HEARTS talks. One row is one talk. talk_key is how a later import finds the same talk, so keep it stable. Leave a cell blank to leave that field as it is. Times can be seconds (90), minutes and seconds (1:30) or hours (1:02:03). status is draft, checked or live. rejected keeps a talk hidden from learners. delete removes the talk. youtube_id is the 11-character YouTube id.</t>
   </si>
@@ -1117,6 +1117,9 @@
   </si>
   <si>
     <t>The speaker says: “Aside for loot Prophet lot for he used to certainly seek strength in the strongest corner” What does that line ask of you this week?</t>
+  </si>
+  <si>
+    <t>The speaker says: “Down repeat it recite it memorize it and it's important in fact to memorize it and teach it to others as” What does that line ask of you this week?</t>
   </si>
   <si>
     <t>The speaker says: “This powerful dua think about it” What does that line ask of you this week?</t>
@@ -3317,7 +3320,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="12" width="14" customWidth="1"/>
@@ -3403,7 +3406,7 @@
         <v>22</v>
       </c>
       <c r="C3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>288</v>
@@ -3432,7 +3435,7 @@
         <v>22</v>
       </c>
       <c r="C4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>288</v>
@@ -3461,7 +3464,7 @@
         <v>34</v>
       </c>
       <c r="C5">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>288</v>
@@ -3490,7 +3493,7 @@
         <v>34</v>
       </c>
       <c r="C6">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>288</v>
@@ -3519,7 +3522,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>288</v>
@@ -3548,7 +3551,7 @@
         <v>268</v>
       </c>
       <c r="C8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>288</v>
@@ -3577,7 +3580,7 @@
         <v>268</v>
       </c>
       <c r="C9">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>288</v>
@@ -3606,7 +3609,7 @@
         <v>268</v>
       </c>
       <c r="C10">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>288</v>
@@ -3635,7 +3638,7 @@
         <v>261</v>
       </c>
       <c r="C11">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>288</v>
@@ -3664,7 +3667,7 @@
         <v>261</v>
       </c>
       <c r="C12">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>288</v>
@@ -3693,7 +3696,7 @@
         <v>261</v>
       </c>
       <c r="C13">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>288</v>
@@ -3722,7 +3725,7 @@
         <v>43</v>
       </c>
       <c r="C14">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>288</v>
@@ -3751,7 +3754,7 @@
         <v>43</v>
       </c>
       <c r="C15">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>288</v>
@@ -3780,7 +3783,7 @@
         <v>43</v>
       </c>
       <c r="C16">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>288</v>
@@ -3809,7 +3812,7 @@
         <v>52</v>
       </c>
       <c r="C17">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>288</v>
@@ -3838,7 +3841,7 @@
         <v>52</v>
       </c>
       <c r="C18">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>288</v>
@@ -3867,7 +3870,7 @@
         <v>52</v>
       </c>
       <c r="C19">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>288</v>
@@ -3896,7 +3899,7 @@
         <v>61</v>
       </c>
       <c r="C20">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>288</v>
@@ -3925,7 +3928,7 @@
         <v>61</v>
       </c>
       <c r="C21">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>288</v>
@@ -3954,7 +3957,7 @@
         <v>69</v>
       </c>
       <c r="C22">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>288</v>
@@ -3983,7 +3986,7 @@
         <v>69</v>
       </c>
       <c r="C23">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>288</v>
@@ -4012,7 +4015,7 @@
         <v>78</v>
       </c>
       <c r="C24">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>288</v>
@@ -4041,7 +4044,7 @@
         <v>78</v>
       </c>
       <c r="C25">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>288</v>
@@ -4070,7 +4073,7 @@
         <v>86</v>
       </c>
       <c r="C26">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>288</v>
@@ -4099,7 +4102,7 @@
         <v>86</v>
       </c>
       <c r="C27">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>288</v>
@@ -4128,7 +4131,7 @@
         <v>93</v>
       </c>
       <c r="C28">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>288</v>
@@ -4157,7 +4160,7 @@
         <v>93</v>
       </c>
       <c r="C29">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>288</v>
@@ -4186,7 +4189,7 @@
         <v>93</v>
       </c>
       <c r="C30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>288</v>
@@ -4215,7 +4218,7 @@
         <v>102</v>
       </c>
       <c r="C31">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>288</v>
@@ -4244,7 +4247,7 @@
         <v>102</v>
       </c>
       <c r="C32">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>288</v>
@@ -4273,7 +4276,7 @@
         <v>109</v>
       </c>
       <c r="C33">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>288</v>
@@ -4302,7 +4305,7 @@
         <v>109</v>
       </c>
       <c r="C34">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>288</v>
@@ -4331,7 +4334,7 @@
         <v>117</v>
       </c>
       <c r="C35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>288</v>
@@ -4360,7 +4363,7 @@
         <v>117</v>
       </c>
       <c r="C36">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>288</v>
@@ -4389,7 +4392,7 @@
         <v>127</v>
       </c>
       <c r="C37">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>288</v>
@@ -4418,7 +4421,7 @@
         <v>127</v>
       </c>
       <c r="C38">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>288</v>
@@ -4447,7 +4450,7 @@
         <v>127</v>
       </c>
       <c r="C39">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>288</v>
@@ -4476,7 +4479,7 @@
         <v>135</v>
       </c>
       <c r="C40">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>288</v>
@@ -4505,7 +4508,7 @@
         <v>135</v>
       </c>
       <c r="C41">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>288</v>
@@ -4534,7 +4537,7 @@
         <v>252</v>
       </c>
       <c r="C42">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>288</v>
@@ -4563,7 +4566,7 @@
         <v>252</v>
       </c>
       <c r="C43">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>288</v>
@@ -4592,7 +4595,7 @@
         <v>252</v>
       </c>
       <c r="C44">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>288</v>
@@ -4621,7 +4624,7 @@
         <v>142</v>
       </c>
       <c r="C45">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>288</v>
@@ -4650,7 +4653,7 @@
         <v>142</v>
       </c>
       <c r="C46">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>288</v>
@@ -4679,7 +4682,7 @@
         <v>142</v>
       </c>
       <c r="C47">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>288</v>
@@ -4708,7 +4711,7 @@
         <v>149</v>
       </c>
       <c r="C48">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>288</v>
@@ -4737,7 +4740,7 @@
         <v>149</v>
       </c>
       <c r="C49">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>288</v>
@@ -4766,7 +4769,7 @@
         <v>157</v>
       </c>
       <c r="C50">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>288</v>
@@ -4795,7 +4798,7 @@
         <v>157</v>
       </c>
       <c r="C51">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>288</v>
@@ -4824,7 +4827,7 @@
         <v>157</v>
       </c>
       <c r="C52">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>288</v>
@@ -4853,7 +4856,7 @@
         <v>166</v>
       </c>
       <c r="C53">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>288</v>
@@ -4882,7 +4885,7 @@
         <v>166</v>
       </c>
       <c r="C54">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>288</v>
@@ -4911,7 +4914,7 @@
         <v>166</v>
       </c>
       <c r="C55">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>288</v>
@@ -4940,7 +4943,7 @@
         <v>174</v>
       </c>
       <c r="C56">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>288</v>
@@ -4969,7 +4972,7 @@
         <v>174</v>
       </c>
       <c r="C57">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>288</v>
@@ -4998,7 +5001,7 @@
         <v>181</v>
       </c>
       <c r="C58">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>288</v>
@@ -5027,7 +5030,7 @@
         <v>181</v>
       </c>
       <c r="C59">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>288</v>
@@ -5056,7 +5059,7 @@
         <v>181</v>
       </c>
       <c r="C60">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>288</v>
@@ -5085,7 +5088,7 @@
         <v>190</v>
       </c>
       <c r="C61">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>288</v>
@@ -5114,7 +5117,7 @@
         <v>190</v>
       </c>
       <c r="C62">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>288</v>
@@ -5143,7 +5146,7 @@
         <v>190</v>
       </c>
       <c r="C63">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>288</v>
@@ -5172,7 +5175,7 @@
         <v>197</v>
       </c>
       <c r="C64">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>288</v>
@@ -5201,7 +5204,7 @@
         <v>197</v>
       </c>
       <c r="C65">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>288</v>
@@ -5230,7 +5233,7 @@
         <v>197</v>
       </c>
       <c r="C66">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>288</v>
@@ -5259,7 +5262,7 @@
         <v>204</v>
       </c>
       <c r="C67">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>288</v>
@@ -5288,7 +5291,7 @@
         <v>204</v>
       </c>
       <c r="C68">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>288</v>
@@ -5317,7 +5320,7 @@
         <v>204</v>
       </c>
       <c r="C69">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>288</v>
@@ -5346,7 +5349,7 @@
         <v>214</v>
       </c>
       <c r="C70">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>288</v>
@@ -5375,7 +5378,7 @@
         <v>214</v>
       </c>
       <c r="C71">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>288</v>
@@ -5404,7 +5407,7 @@
         <v>214</v>
       </c>
       <c r="C72">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>288</v>
@@ -5433,7 +5436,7 @@
         <v>221</v>
       </c>
       <c r="C73">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>288</v>
@@ -5462,7 +5465,7 @@
         <v>221</v>
       </c>
       <c r="C74">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>288</v>
@@ -5491,7 +5494,7 @@
         <v>229</v>
       </c>
       <c r="C75">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>288</v>
@@ -5520,7 +5523,7 @@
         <v>229</v>
       </c>
       <c r="C76">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>288</v>
@@ -5549,7 +5552,7 @@
         <v>238</v>
       </c>
       <c r="C77">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>288</v>
@@ -5578,7 +5581,7 @@
         <v>238</v>
       </c>
       <c r="C78">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>288</v>
@@ -5607,7 +5610,7 @@
         <v>238</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>288</v>
@@ -5636,13 +5639,13 @@
         <v>245</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>288</v>
       </c>
       <c r="E80">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>368</v>
@@ -5659,28 +5662,31 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E81">
+        <v>30</v>
+      </c>
+      <c r="F81" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="E81">
-        <v>262</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="N81" s="3" t="s">
-        <v>371</v>
+        <v>290</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>372</v>
+        <v>31</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
@@ -5691,22 +5697,22 @@
         <v>252</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>288</v>
+        <v>370</v>
       </c>
       <c r="E82">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="F82" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="O82" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="N82" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="O82" s="3" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
@@ -5717,83 +5723,109 @@
         <v>252</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D83" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E83">
+        <v>158</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="E83">
-        <v>22</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="N83" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>288</v>
+        <v>375</v>
       </c>
       <c r="E84">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="F84" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I84" s="3" t="s">
         <v>379</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>288</v>
       </c>
       <c r="E85">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>380</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O85" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E86">
+        <v>300</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="N86" s="3" t="s">
         <v>372</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -5816,7 +5848,7 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5828,13 +5860,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>19</v>

--- a/hearts-prototype/artifacts/hearts-master-sheet-example.xlsx
+++ b/hearts-prototype/artifacts/hearts-master-sheet-example.xlsx
@@ -7,15 +7,16 @@
     <sheet sheetId="1" name="Talks" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Questions" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Resources" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="CircleAnswers" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="386">
-  <si>
-    <t>HEARTS talks. One row is one talk. talk_key is how a later import finds the same talk, so keep it stable. Leave a cell blank to leave that field as it is. Times can be seconds (90), minutes and seconds (1:30) or hours (1:02:03). status is draft, checked or live. rejected keeps a talk hidden from learners. delete removes the talk. youtube_id is the 11-character YouTube id.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="451">
+  <si>
+    <t>HEARTS talks. One row is one talk. talk_key is how a later import finds the same talk, so keep it stable. Leave a cell blank to leave that field as it is. Times can be seconds (90), minutes and seconds (1:30) or hours (1:02:03). status is draft, checked or live. rejected keeps a talk hidden from learners. delete removes the talk. youtube_id is the 11-character YouTube id. provider is youtube, vimeo or file. A Vimeo talk puts the number in vimeo_id. An uploaded film puts the media id in media_id. duration is the length in seconds. transcript is the speaker's words and is only for captions that fit in the cell (under 30,000 characters); a longer transcript is a Resources row with kind transcript and a media_id. hook_text, turn_text, land_text and transcript are the speaker's words: the kill list is not applied to them. notes is our own writing and may contain plain text such as conf=high. A hors d'oeuvre is usually 15 to 20 seconds. Up to the cap on the master desk (45 seconds unless that cap is changed) is allowed and only warned about. Shorter than 15, or longer than the cap, is refused. app_in and app_out are one continuous appetiser. hook_in and hook_out, turn_in and turn_out, land_in and land_out are up to three separate cuts. The player plays them in that order, and their lengths together stay within about 3 minutes (195 seconds).</t>
   </si>
   <si>
     <t>talk_key</t>
@@ -63,6 +64,24 @@
     <t>app_out</t>
   </si>
   <si>
+    <t>hook_in</t>
+  </si>
+  <si>
+    <t>hook_out</t>
+  </si>
+  <si>
+    <t>turn_in</t>
+  </si>
+  <si>
+    <t>turn_out</t>
+  </si>
+  <si>
+    <t>land_in</t>
+  </si>
+  <si>
+    <t>land_out</t>
+  </si>
+  <si>
     <t>hook_text</t>
   </si>
   <si>
@@ -78,6 +97,21 @@
     <t>notes</t>
   </si>
   <si>
+    <t>provider</t>
+  </si>
+  <si>
+    <t>vimeo_id</t>
+  </si>
+  <si>
+    <t>media_id</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>transcript</t>
+  </si>
+  <si>
     <t>yt-MK5q_zMiX1g</t>
   </si>
   <si>
@@ -840,7 +874,7 @@
     <t>Draft, needs a human check. Times and lines come from the captions by machine. Appetiser 1:33:45 to 1:36:07.</t>
   </si>
   <si>
-    <t>HEARTS pop-up questions. Name the talk with talk_key or youtube_id. Leave question_id blank to add a question, or fill it in to change that question. type is free text, multiple choice, reflection or task. status is draft or approved (approved is what learners meet in the main). source is ai or human. A blank cell leaves that field as it is. delete removes the question. Times use the same forms as the Talks tab and must fall inside the talk.</t>
+    <t>HEARTS questions. Name the talk with talk_key or youtube_id. The export writes question_id, and an import with that id updates the same question. A row with no question_id is matched to a question on the same talk with the same time and the same text, so importing the same file again does not add a copy. Leave question_id blank only when the question is new. type is free text, multiple choice, reflection or task. status is draft or approved (approved is what learners meet). source is ai or human. A blank cell leaves that field as it is. delete removes the question. Times use the same forms as the Talks tab and must fall inside the talk. type task is an activation task: due_days is how many days the learner has (1 to 366), evidence is none, note or photo, and show_imam is yes when the imam should see it. place is popup or workbook. A workbook row is a reflection kept in the workbook rather than a pop-up in the film. Questions, choices and notes are our own writing. Notes may contain plain text such as conf=high.</t>
   </si>
   <si>
     <t>question_id</t>
@@ -879,6 +913,18 @@
     <t>source</t>
   </si>
   <si>
+    <t>due_days</t>
+  </si>
+  <si>
+    <t>evidence</t>
+  </si>
+  <si>
+    <t>show_imam</t>
+  </si>
+  <si>
+    <t>place</t>
+  </si>
+  <si>
     <t>reflection</t>
   </si>
   <si>
@@ -1161,7 +1207,7 @@
     <t>Which one manner of the Prophet would you like to carry with you this week?</t>
   </si>
   <si>
-    <t>HEARTS resources, one link per row. talk_key names the talk. The same talk_key and label updates that link next time. url must start with https://. kind is link or file. Leave status blank to keep the link, or put delete to remove it.</t>
+    <t>HEARTS resources, one row per item. talk_key names the talk. The same talk_key and label updates that row next time. kind is link, file, summary, quote, reading, guide or transcript. url must start with https:// for a link, and for a file that is not an upload. A file row may instead put an uploaded file's number in media_id. kind transcript points at an uploaded text file (media_id) so a transcript longer than 30,000 characters can come in as a file rather than a cell; that file is copied onto the talk. summary, reading and guide are our own writing. quote and transcript are the speaker's words, so the kill list is not applied to them. A reading row is a suggestion to verify, not a link that has been checked. Leave status blank to keep the row, or put delete to remove it.</t>
   </si>
   <si>
     <t>label</t>
@@ -1171,6 +1217,156 @@
   </si>
   <si>
     <t>kind</t>
+  </si>
+  <si>
+    <t>body</t>
+  </si>
+  <si>
+    <t>HEARTS circle answers. One row is one answer shown under a question in “What others said” until real answers arrive. question_id is the number from the Questions tab. Leave circle_id blank to add an answer, or fill it in to change that answer. tone is warm, honest, practical, searching or quiet. length is short, medium or long. origin is ai or staff. enabled is yes or no. Put delete in status to remove the answer. Circle answers are never counted as answers.</t>
+  </si>
+  <si>
+    <t>circle_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>tone</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>enabled</t>
+  </si>
+  <si>
+    <t>Safiya</t>
+  </si>
+  <si>
+    <t>Done, quietly. I listened to that part twice.</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Sami</t>
+  </si>
+  <si>
+    <t>Tried it once and noticed I was rushing it.</t>
+  </si>
+  <si>
+    <t>searching</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>Noor</t>
+  </si>
+  <si>
+    <t>Did it straight after Maghrib so it would not slip. I tied it to something I already do every day, so I do not forget. Small, but it is a start.</t>
+  </si>
+  <si>
+    <t>practical</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>Idris</t>
+  </si>
+  <si>
+    <t>Missed the first day, managed the second. My days are full and this is the first thing that slips.</t>
+  </si>
+  <si>
+    <t>honest</t>
+  </si>
+  <si>
+    <t>Ruqayyah</t>
+  </si>
+  <si>
+    <t>Did this with my little brother, which made it easier.</t>
+  </si>
+  <si>
+    <t>warm</t>
+  </si>
+  <si>
+    <t>Just this: slow down. The line about the heart is the one I wrote down.</t>
+  </si>
+  <si>
+    <t>I keep coming back to the words he used.</t>
+  </si>
+  <si>
+    <t>I tried it on the bus to work this morning. Two minutes, no more, so it is easy to keep going. Day two went better than day one.</t>
+  </si>
+  <si>
+    <t>I will be straight: this one was hard to answer. I talk about it more than I live it, and this caught me out.</t>
+  </si>
+  <si>
+    <t>Musa</t>
+  </si>
+  <si>
+    <t>This one landed gently for me.</t>
+  </si>
+  <si>
+    <t>I went with “You feel no more sadness”. It just fitted. I listened to that part twice.</t>
+  </si>
+  <si>
+    <t>I went with “You start to incline towards the Akhira”. I am not certain, but it matched the part I replayed.</t>
+  </si>
+  <si>
+    <t>I went with “You stop making mistakes”. It is the one I can actually act on this week. I tied it to something I already do every day, so I do not forget. Small, but it is a start.</t>
+  </si>
+  <si>
+    <t>I went with “You feel no more sadness”. I went back and forth, but this is the one I can stand behind. My days are full and this is the first thing that slips.</t>
+  </si>
+  <si>
+    <t>Hana</t>
+  </si>
+  <si>
+    <t>I went with “You start to incline towards the Akhira”. It felt like the kindest reading of what he said.</t>
+  </si>
+  <si>
+    <t>Saying less tonight, but this stayed with me. The line about the heart is the one I wrote down.</t>
+  </si>
+  <si>
+    <t>I do not have a neat answer yet.</t>
+  </si>
+  <si>
+    <t>I wrote it on a sticky note by the kettle. Two minutes, no more, so it is easy to keep going. Day two went better than day one.</t>
+  </si>
+  <si>
+    <t>I nearly skipped this one, then came back. I talk about it more than I live it, and this caught me out.</t>
+  </si>
+  <si>
+    <t>Khalid</t>
+  </si>
+  <si>
+    <t>What a kind way to put it.</t>
+  </si>
+  <si>
+    <t>A small yes from me. I listened to that part twice.</t>
+  </si>
+  <si>
+    <t>I am still turning this over.</t>
+  </si>
+  <si>
+    <t>I picked one small thing and did it the same day. I tied it to something I already do every day, so I do not forget. Small, but it is a start.</t>
+  </si>
+  <si>
+    <t>If I am truthful, I keep putting this off. My days are full and this is the first thing that slips.</t>
+  </si>
+  <si>
+    <t>Layla</t>
+  </si>
+  <si>
+    <t>I smiled at this, because it felt close to home.</t>
   </si>
 </sst>
 </file>
@@ -1562,15 +1758,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:AE33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="20" width="14" customWidth="1"/>
+    <col min="11" max="31" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="48" customHeight="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1593,8 +1789,19 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+    </row>
+    <row r="2" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1655,31 +1862,64 @@
       <c r="T2" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H3">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L3">
         <v>12.12</v>
@@ -1693,46 +1933,49 @@
       <c r="O3">
         <v>97.57</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H4">
         <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="L4">
         <v>74.48</v>
@@ -1746,46 +1989,49 @@
       <c r="O4">
         <v>627.29</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD4">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H5">
         <v>27</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L5">
         <v>1489.96</v>
@@ -1799,46 +2045,49 @@
       <c r="O5">
         <v>931.97</v>
       </c>
-      <c r="P5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD5">
+        <v>3403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H6">
         <v>26</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L6">
         <v>288.6</v>
@@ -1852,46 +2101,49 @@
       <c r="O6">
         <v>212.8</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD6">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H7">
         <v>25</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L7">
         <v>98.36</v>
@@ -1905,46 +2157,49 @@
       <c r="O7">
         <v>124.68</v>
       </c>
-      <c r="P7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H8">
         <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L8">
         <v>1961.16</v>
@@ -1958,46 +2213,49 @@
       <c r="O8">
         <v>1592.6</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD8">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H9">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L9">
         <v>111.86</v>
@@ -2011,46 +2269,49 @@
       <c r="O9">
         <v>156.72</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H10">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L10">
         <v>35.33</v>
@@ -2064,46 +2325,49 @@
       <c r="O10">
         <v>307.56</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD10">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H11">
         <v>21</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="L11">
         <v>164.76</v>
@@ -2117,46 +2381,49 @@
       <c r="O11">
         <v>1114.12</v>
       </c>
-      <c r="P11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD11">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H12">
         <v>20</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="L12">
         <v>135.76</v>
@@ -2170,46 +2437,49 @@
       <c r="O12">
         <v>217.12</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD12">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H13">
         <v>19</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="L13">
         <v>57.52</v>
@@ -2223,46 +2493,49 @@
       <c r="O13">
         <v>115.8</v>
       </c>
-      <c r="P13" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD13">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H14">
         <v>18</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="L14">
         <v>0.06</v>
@@ -2276,46 +2549,49 @@
       <c r="O14">
         <v>161.66</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V14" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AD14">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H15">
         <v>17</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="L15">
         <v>590.64</v>
@@ -2329,46 +2605,49 @@
       <c r="O15">
         <v>691.44</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD15">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H16">
         <v>16</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="L16">
         <v>44.86</v>
@@ -2382,46 +2661,49 @@
       <c r="O16">
         <v>256.22</v>
       </c>
-      <c r="P16" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z16" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD16">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H17">
         <v>14</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L17">
         <v>1733.92</v>
@@ -2435,46 +2717,49 @@
       <c r="O17">
         <v>538.27</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD17">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H18">
         <v>13</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L18">
         <v>22.91</v>
@@ -2488,46 +2773,49 @@
       <c r="O18">
         <v>134.68</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V18" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD18">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H19">
         <v>12</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="L19">
         <v>1893.44</v>
@@ -2541,46 +2829,49 @@
       <c r="O19">
         <v>1212.24</v>
       </c>
-      <c r="P19" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V19" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD19">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H20">
         <v>11</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="L20">
         <v>1904.36</v>
@@ -2594,46 +2885,49 @@
       <c r="O20">
         <v>458.23</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V20" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="AD20">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="L21">
         <v>4.34</v>
@@ -2647,46 +2941,49 @@
       <c r="O21">
         <v>144.36</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V21" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD21">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H22">
         <v>9</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="L22">
         <v>328.79</v>
@@ -2700,46 +2997,49 @@
       <c r="O22">
         <v>2126.64</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V22" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD22">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H23">
         <v>8</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="L23">
         <v>2222.08</v>
@@ -2753,46 +3053,49 @@
       <c r="O23">
         <v>1215.92</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="AD23">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H24">
         <v>7</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="L24">
         <v>223.23</v>
@@ -2806,46 +3109,49 @@
       <c r="O24">
         <v>172.88</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V24" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD24">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H25">
         <v>6</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="L25">
         <v>678.68</v>
@@ -2859,46 +3165,49 @@
       <c r="O25">
         <v>4086</v>
       </c>
-      <c r="P25" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V25" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z25" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD25">
+        <v>4401</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H26">
         <v>5</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="L26">
         <v>1481.34</v>
@@ -2912,46 +3221,49 @@
       <c r="O26">
         <v>5006.62</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V26" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AD26">
+        <v>5821</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H27">
         <v>4</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="L27">
         <v>21.32</v>
@@ -2965,46 +3277,49 @@
       <c r="O27">
         <v>175.57</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V27" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="AD27">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H28">
         <v>3</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="L28">
         <v>423.23</v>
@@ -3018,46 +3333,49 @@
       <c r="O28">
         <v>381.64</v>
       </c>
-      <c r="P28" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V28" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z28" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="AD28">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H29">
         <v>2</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="L29">
         <v>892.94</v>
@@ -3071,46 +3389,49 @@
       <c r="O29">
         <v>1029.4</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V29" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="AD29">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="L30">
         <v>15.52</v>
@@ -3124,46 +3445,49 @@
       <c r="O30">
         <v>47.48</v>
       </c>
-      <c r="P30" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V30" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="W30" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="X30" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="Y30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z30" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD30">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="J31">
         <v>26</v>
@@ -3180,46 +3504,49 @@
       <c r="O31">
         <v>431</v>
       </c>
-      <c r="P31" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V31" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="W31" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="X31" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z31" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="AD31">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J32">
         <v>22</v>
@@ -3236,46 +3563,49 @@
       <c r="O32">
         <v>929.04</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T32" s="3" t="s">
+      <c r="V32" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="AD32">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>266</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J33">
         <v>3</v>
@@ -3292,26 +3622,29 @@
       <c r="O33">
         <v>5767.19</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>274</v>
+      <c r="V33" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="AD33">
+        <v>10124</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T2"/>
+  <autoFilter ref="A2:AE2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A1:AE1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3320,17 +3653,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:T86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="16" width="14" customWidth="1"/>
+    <col min="14" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="48" customHeight="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3347,8 +3680,12 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3356,2482 +3693,2494 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>84</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E3">
         <v>90</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C4">
         <v>83</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C5">
         <v>82</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E5">
         <v>1494</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C6">
         <v>81</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E6">
         <v>941</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C7">
         <v>80</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E7">
         <v>124</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C8">
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E8">
         <v>9172</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C9">
         <v>78</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E9">
         <v>3831</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C10">
         <v>77</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E10">
         <v>1485</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C11">
         <v>76</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E11">
         <v>1569</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C12">
         <v>75</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E12">
         <v>1359</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C13">
         <v>74</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E13">
         <v>368</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C14">
         <v>73</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E14">
         <v>2605</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C15">
         <v>72</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E15">
         <v>1553</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>71</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E16">
         <v>1035</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C17">
         <v>70</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E17">
         <v>382</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C18">
         <v>69</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E18">
         <v>319</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C19">
         <v>68</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E19">
         <v>109</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C20">
         <v>67</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E20">
         <v>99</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C21">
         <v>66</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E21">
         <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C22">
         <v>65</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E22">
         <v>735</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E23">
         <v>633</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C24">
         <v>63</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E24">
         <v>94</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C25">
         <v>62</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E25">
         <v>18</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C26">
         <v>61</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E26">
         <v>323</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C27">
         <v>60</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E27">
         <v>73</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C28">
         <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E28">
         <v>1212</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C29">
         <v>58</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E29">
         <v>732</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C30">
         <v>57</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E30">
         <v>328</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C31">
         <v>56</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E31">
         <v>140</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C32">
         <v>55</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E32">
         <v>74</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C33">
         <v>54</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E33">
         <v>62</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C34">
         <v>53</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E34">
         <v>7</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C35">
         <v>52</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E35">
         <v>189</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C36">
         <v>51</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E36">
         <v>93</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C37">
         <v>50</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E37">
         <v>1830</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C38">
         <v>49</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E38">
         <v>1378</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C39">
         <v>48</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E39">
         <v>413</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C40">
         <v>47</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E40">
         <v>411</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C41">
         <v>46</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E41">
         <v>40</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C42">
         <v>45</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E42">
         <v>2072</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C43">
         <v>44</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E43">
         <v>1170</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E44">
         <v>110</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C45">
         <v>42</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E45">
         <v>2129</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C46">
         <v>41</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E46">
         <v>1009</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C47">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E47">
         <v>215</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C48">
         <v>39</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E48">
         <v>139</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C49">
         <v>38</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E49">
         <v>31</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C50">
         <v>37</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E50">
         <v>2794</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C51">
         <v>36</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E51">
         <v>1901</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C52">
         <v>35</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E52">
         <v>887</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C53">
         <v>34</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E53">
         <v>1768</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C54">
         <v>33</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E54">
         <v>902</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C55">
         <v>32</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E55">
         <v>256</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C56">
         <v>31</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E56">
         <v>152</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C57">
         <v>30</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E57">
         <v>5</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C58">
         <v>29</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E58">
         <v>2416</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C59">
         <v>28</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E59">
         <v>1280</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C60">
         <v>27</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E60">
         <v>333</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="C61">
         <v>26</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E61">
         <v>2237</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="C62">
         <v>25</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E62">
         <v>1634</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="C63">
         <v>24</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E63">
         <v>636</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="C64">
         <v>23</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E64">
         <v>311</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="C65">
         <v>22</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E65">
         <v>181</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="C66">
         <v>21</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E66">
         <v>58</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C67">
         <v>20</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E67">
         <v>4179</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C68">
         <v>19</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E68">
         <v>2249</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C69">
         <v>18</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E69">
         <v>643</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C70">
         <v>17</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E70">
         <v>5328</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C71">
         <v>16</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E71">
         <v>3081</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C72">
         <v>15</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E72">
         <v>1243</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C73">
         <v>14</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E73">
         <v>287</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C74">
         <v>13</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E74">
         <v>37</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="C75">
         <v>12</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E75">
         <v>382</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="C76">
         <v>11</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E76">
         <v>66</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C77">
         <v>10</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E77">
         <v>889</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C78">
         <v>9</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E78">
         <v>584</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C79">
         <v>8</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E79">
         <v>93</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C80">
         <v>7</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E80">
         <v>38</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C81">
         <v>6</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E81">
         <v>30</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C82">
         <v>5</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="E82">
         <v>262</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C83">
         <v>4</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E83">
         <v>158</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C84">
         <v>3</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="E84">
         <v>22</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E85">
         <v>120</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E86">
         <v>300</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P2"/>
+  <autoFilter ref="A2:T2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:T1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5840,42 +6189,918 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="5" width="14" customWidth="1"/>
+    <col min="1" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="48" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:G2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="11" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
         <v>19</v>
       </c>
+      <c r="E9" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>17</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>15</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>12</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>9</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>412</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E2"/>
+  <autoFilter ref="A2:K2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/hearts-prototype/artifacts/hearts-master-sheet-example.xlsx
+++ b/hearts-prototype/artifacts/hearts-master-sheet-example.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="451">
-  <si>
-    <t>HEARTS talks. One row is one talk. talk_key is how a later import finds the same talk, so keep it stable. Leave a cell blank to leave that field as it is. Times can be seconds (90), minutes and seconds (1:30) or hours (1:02:03). status is draft, checked or live. rejected keeps a talk hidden from learners. delete removes the talk. youtube_id is the 11-character YouTube id. provider is youtube, vimeo or file. A Vimeo talk puts the number in vimeo_id. An uploaded film puts the media id in media_id. duration is the length in seconds. transcript is the speaker's words and is only for captions that fit in the cell (under 30,000 characters); a longer transcript is a Resources row with kind transcript and a media_id. hook_text, turn_text, land_text and transcript are the speaker's words: the kill list is not applied to them. notes is our own writing and may contain plain text such as conf=high. A hors d'oeuvre is usually 15 to 20 seconds. Up to the cap on the master desk (45 seconds unless that cap is changed) is allowed and only warned about. Shorter than 15, or longer than the cap, is refused. app_in and app_out are one continuous appetiser. hook_in and hook_out, turn_in and turn_out, land_in and land_out are up to three separate cuts. The player plays them in that order, and their lengths together stay within about 3 minutes (195 seconds).</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="452">
+  <si>
+    <t>HEARTS talks. One row is one talk. talk_key is how a later import finds the same talk, so keep it stable. Leave a cell blank to leave that field as it is. Times can be seconds (90), minutes and seconds (1:30) or hours (1:02:03). status is draft, checked or live. rejected keeps a talk hidden from learners. delete removes the talk. youtube_id is the 11-character YouTube id. provider is youtube, vimeo or file. A Vimeo talk puts the number in vimeo_id. An uploaded film puts the media id in media_id. duration is the length in seconds. transcript is the speaker's words and is only for captions that fit in the cell (under 30,000 characters); a longer transcript is a Resources row with kind transcript and a media_id. hook_text, turn_text, land_text and transcript are the speaker's words: the kill list is not applied to them. notes is our own writing and may contain plain text such as conf=high. A hors d'oeuvre is usually 15 to 20 seconds. Up to the cap on the master desk (45 seconds unless that cap is changed) is allowed and only warned about. Shorter than 15, or longer than the cap, is refused. app_in and app_out are one continuous appetiser. hook_in and hook_out, turn_in and turn_out, land_in and land_out are up to three separate cuts. The player plays them in that order, and their lengths together stay within about 3 minutes (195 seconds). pack is optional: the name or number of a course pack that already exists, and the talk's course joins it, so people who join with that pack's codes get the course. A portal admin can only name their own portal's packs. A blank pack leaves packs as they are, and the export leaves it blank.</t>
   </si>
   <si>
     <t>talk_key</t>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>transcript</t>
+  </si>
+  <si>
+    <t>pack</t>
   </si>
   <si>
     <t>yt-MK5q_zMiX1g</t>
@@ -1758,15 +1761,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE33"/>
+  <dimension ref="A1:AF33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="31" width="14" customWidth="1"/>
+    <col min="11" max="32" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="48" customHeight="1" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1800,8 +1803,9 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
-    </row>
-    <row r="2" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF1" s="1"/>
+    </row>
+    <row r="2" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1895,31 +1899,34 @@
       <c r="AE2" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF2" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L3">
         <v>12.12</v>
@@ -1934,48 +1941,48 @@
         <v>97.57</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AD3">
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4">
         <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L4">
         <v>74.48</v>
@@ -1990,48 +1997,48 @@
         <v>627.29</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AD4">
         <v>1654</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5">
         <v>27</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L5">
         <v>1489.96</v>
@@ -2046,48 +2053,48 @@
         <v>931.97</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AD5">
         <v>3403</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6">
         <v>26</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L6">
         <v>288.6</v>
@@ -2102,48 +2109,48 @@
         <v>212.8</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AD6">
         <v>541</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7">
         <v>25</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L7">
         <v>98.36</v>
@@ -2158,48 +2165,48 @@
         <v>124.68</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD7">
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8">
         <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L8">
         <v>1961.16</v>
@@ -2214,48 +2221,48 @@
         <v>1592.6</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AD8">
         <v>2140</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H9">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L9">
         <v>111.86</v>
@@ -2270,48 +2277,48 @@
         <v>156.72</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z9" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD9">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L10">
         <v>35.33</v>
@@ -2326,48 +2333,48 @@
         <v>307.56</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z10" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AD10">
         <v>397</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="G11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H11">
         <v>21</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L11">
         <v>164.76</v>
@@ -2382,48 +2389,48 @@
         <v>1114.12</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AD11">
         <v>1710</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H12">
         <v>20</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L12">
         <v>135.76</v>
@@ -2438,48 +2445,48 @@
         <v>217.12</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AD12">
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H13">
         <v>19</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L13">
         <v>57.52</v>
@@ -2494,48 +2501,48 @@
         <v>115.8</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD13">
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H14">
         <v>18</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L14">
         <v>0.06</v>
@@ -2550,48 +2557,48 @@
         <v>161.66</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Y14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z14" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD14">
         <v>227</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="G15" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H15">
         <v>17</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L15">
         <v>590.64</v>
@@ -2606,48 +2613,48 @@
         <v>691.44</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y15" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z15" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AD15">
         <v>2089</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H16">
         <v>16</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L16">
         <v>44.86</v>
@@ -2662,48 +2669,48 @@
         <v>256.22</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y16" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z16" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AD16">
         <v>412</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H17">
         <v>14</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L17">
         <v>1733.92</v>
@@ -2718,48 +2725,48 @@
         <v>538.27</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y17" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z17" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD17">
         <v>2424</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H18">
         <v>13</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L18">
         <v>22.91</v>
@@ -2774,48 +2781,48 @@
         <v>134.68</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z18" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AD18">
         <v>230</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="G19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H19">
         <v>12</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L19">
         <v>1893.44</v>
@@ -2830,48 +2837,48 @@
         <v>1212.24</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z19" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AD19">
         <v>3600</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H20">
         <v>11</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L20">
         <v>1904.36</v>
@@ -2886,48 +2893,48 @@
         <v>458.23</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y20" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z20" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AD20">
         <v>2594</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L21">
         <v>4.34</v>
@@ -2942,48 +2949,48 @@
         <v>144.36</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z21" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AD21">
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H22">
         <v>9</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L22">
         <v>328.79</v>
@@ -2998,48 +3005,48 @@
         <v>2126.64</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z22" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD22">
         <v>3137</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H23">
         <v>8</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L23">
         <v>2222.08</v>
@@ -3054,48 +3061,48 @@
         <v>1215.92</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z23" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AD23">
         <v>2781</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H24">
         <v>7</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L24">
         <v>223.23</v>
@@ -3110,48 +3117,48 @@
         <v>172.88</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z24" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AD24">
         <v>394</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H25">
         <v>6</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L25">
         <v>678.68</v>
@@ -3166,48 +3173,48 @@
         <v>4086</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z25" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AD25">
         <v>4401</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H26">
         <v>5</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L26">
         <v>1481.34</v>
@@ -3222,48 +3229,48 @@
         <v>5006.62</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y26" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z26" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AD26">
         <v>5821</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H27">
         <v>4</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L27">
         <v>21.32</v>
@@ -3278,48 +3285,48 @@
         <v>175.57</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z27" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AD27">
         <v>443</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H28">
         <v>3</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L28">
         <v>423.23</v>
@@ -3334,48 +3341,48 @@
         <v>381.64</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z28" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AD28">
         <v>763</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H29">
         <v>2</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L29">
         <v>892.94</v>
@@ -3390,48 +3397,48 @@
         <v>1029.4</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z29" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AD29">
         <v>1183</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L30">
         <v>15.52</v>
@@ -3446,48 +3453,48 @@
         <v>47.48</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y30" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z30" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AD30">
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>264</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J31">
         <v>26</v>
@@ -3505,48 +3512,48 @@
         <v>431</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y31" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z31" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AD31">
         <v>2861</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J32">
         <v>22</v>
@@ -3564,48 +3571,48 @@
         <v>929.04</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z32" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AD32">
         <v>2337</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D33" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>280</v>
-      </c>
       <c r="G33" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J33">
         <v>3</v>
@@ -3623,28 +3630,28 @@
         <v>5767.19</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Y33" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z33" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AD33">
         <v>10124</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AE2"/>
+  <autoFilter ref="A2:AF2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:AE1"/>
+    <mergeCell ref="A1:AF1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3663,7 +3670,7 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3693,40 +3700,40 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>25</v>
@@ -3735,2446 +3742,2446 @@
         <v>26</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>84</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E3">
         <v>90</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>83</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5">
         <v>82</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E5">
         <v>1494</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6">
         <v>81</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E6">
         <v>941</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7">
         <v>80</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E7">
         <v>124</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C8">
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E8">
         <v>9172</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C9">
         <v>78</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E9">
         <v>3831</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C10">
         <v>77</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E10">
         <v>1485</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C11">
         <v>76</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E11">
         <v>1569</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C12">
         <v>75</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E12">
         <v>1359</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C13">
         <v>74</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E13">
         <v>368</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>73</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E14">
         <v>2605</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15">
         <v>72</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E15">
         <v>1553</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16">
         <v>71</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E16">
         <v>1035</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17">
         <v>70</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E17">
         <v>382</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18">
         <v>69</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E18">
         <v>319</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C19">
         <v>68</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E19">
         <v>109</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>67</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E20">
         <v>99</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21">
         <v>66</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E21">
         <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22">
         <v>65</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E22">
         <v>735</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23">
         <v>64</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E23">
         <v>633</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <v>63</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E24">
         <v>94</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25">
         <v>62</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E25">
         <v>18</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26">
         <v>61</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E26">
         <v>323</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27">
         <v>60</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E27">
         <v>73</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28">
         <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E28">
         <v>1212</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C29">
         <v>58</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E29">
         <v>732</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30">
         <v>57</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E30">
         <v>328</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C31">
         <v>56</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E31">
         <v>140</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C32">
         <v>55</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E32">
         <v>74</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C33">
         <v>54</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E33">
         <v>62</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C34">
         <v>53</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E34">
         <v>7</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C35">
         <v>52</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E35">
         <v>189</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C36">
         <v>51</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E36">
         <v>93</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C37">
         <v>50</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E37">
         <v>1830</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C38">
         <v>49</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E38">
         <v>1378</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C39">
         <v>48</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E39">
         <v>413</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C40">
         <v>47</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E40">
         <v>411</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C41">
         <v>46</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E41">
         <v>40</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C42">
         <v>45</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E42">
         <v>2072</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C43">
         <v>44</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E43">
         <v>1170</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C44">
         <v>43</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E44">
         <v>110</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C45">
         <v>42</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E45">
         <v>2129</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C46">
         <v>41</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E46">
         <v>1009</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C47">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E47">
         <v>215</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C48">
         <v>39</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E48">
         <v>139</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C49">
         <v>38</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E49">
         <v>31</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C50">
         <v>37</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E50">
         <v>2794</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C51">
         <v>36</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E51">
         <v>1901</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C52">
         <v>35</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E52">
         <v>887</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C53">
         <v>34</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E53">
         <v>1768</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C54">
         <v>33</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E54">
         <v>902</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C55">
         <v>32</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E55">
         <v>256</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C56">
         <v>31</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E56">
         <v>152</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C57">
         <v>30</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E57">
         <v>5</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C58">
         <v>29</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E58">
         <v>2416</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C59">
         <v>28</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E59">
         <v>1280</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C60">
         <v>27</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E60">
         <v>333</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C61">
         <v>26</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E61">
         <v>2237</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C62">
         <v>25</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E62">
         <v>1634</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C63">
         <v>24</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E63">
         <v>636</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C64">
         <v>23</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E64">
         <v>311</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C65">
         <v>22</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E65">
         <v>181</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C66">
         <v>21</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E66">
         <v>58</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C67">
         <v>20</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E67">
         <v>4179</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C68">
         <v>19</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E68">
         <v>2249</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C69">
         <v>18</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E69">
         <v>643</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C70">
         <v>17</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E70">
         <v>5328</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C71">
         <v>16</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E71">
         <v>3081</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C72">
         <v>15</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E72">
         <v>1243</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C73">
         <v>14</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E73">
         <v>287</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C74">
         <v>13</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E74">
         <v>37</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C75">
         <v>12</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E75">
         <v>382</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C76">
         <v>11</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E76">
         <v>66</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C77">
         <v>10</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E77">
         <v>889</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C78">
         <v>9</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E78">
         <v>584</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C79">
         <v>8</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E79">
         <v>93</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C80">
         <v>7</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E80">
         <v>38</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C81">
         <v>6</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E81">
         <v>30</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C82">
         <v>5</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E82">
         <v>262</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C83">
         <v>4</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E83">
         <v>158</v>
       </c>
       <c r="F83" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="O83" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C84">
         <v>3</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E84">
         <v>22</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E85">
         <v>120</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E86">
         <v>300</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -6197,7 +6204,7 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6211,19 +6218,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>29</v>
@@ -6249,7 +6256,7 @@
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6270,28 +6277,28 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>25</v>
@@ -6299,10 +6306,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -6311,30 +6318,30 @@
         <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -6343,30 +6350,30 @@
         <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -6375,30 +6382,30 @@
         <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -6407,30 +6414,30 @@
         <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -6439,30 +6446,30 @@
         <v>21</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -6471,30 +6478,30 @@
         <v>20</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -6503,30 +6510,30 @@
         <v>19</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>416</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -6535,30 +6542,30 @@
         <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>420</v>
-      </c>
       <c r="I10" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -6567,30 +6574,30 @@
         <v>17</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>423</v>
-      </c>
       <c r="H11" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -6599,30 +6606,30 @@
         <v>16</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -6631,30 +6638,30 @@
         <v>15</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -6663,30 +6670,30 @@
         <v>14</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -6695,30 +6702,30 @@
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -6727,30 +6734,30 @@
         <v>12</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -6759,30 +6766,30 @@
         <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -6791,30 +6798,30 @@
         <v>10</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -6823,30 +6830,30 @@
         <v>9</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -6855,30 +6862,30 @@
         <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -6887,30 +6894,30 @@
         <v>7</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -6919,30 +6926,30 @@
         <v>6</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -6951,30 +6958,30 @@
         <v>5</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -6983,30 +6990,30 @@
         <v>4</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -7015,30 +7022,30 @@
         <v>3</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -7047,30 +7054,30 @@
         <v>2</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -7079,22 +7086,22 @@
         <v>1</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
